--- a/demo-data/Deal_Request_Form.xlsx
+++ b/demo-data/Deal_Request_Form.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deal Request Form" sheetId="1" r:id="R2c6d626df2974482"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation Lists" sheetId="2" r:id="R1ee62800611d44c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Data" sheetId="3" r:id="R9adfd284aae94be2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deal Request Form" sheetId="1" r:id="R748a7a923e5c4b53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation Lists" sheetId="2" r:id="Red8e8ac4c65041e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Data" sheetId="3" r:id="R2fbe17a58c2e4132"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -479,7 +479,7 @@
     </x:row>
     <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>Fill only yellow user-input fields. Reference-driven fields are populated from master data. Review the calculated summary before submitting.</x:v>
+        <x:v>Fill only yellow user-input fields. Requested Total Discount % is the complete customer-facing discount from Gross Price. Base Rebate is reference data and is already reflected in Gross Price.</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -704,13 +704,13 @@
         <x:v>Gross Price</x:v>
       </x:c>
       <x:c r="F17" s="30" t="str">
-        <x:v>Base Discount %</x:v>
+        <x:v>Base Rebate % (Reference)</x:v>
       </x:c>
       <x:c r="G17" s="30" t="str">
         <x:v>Current Net Price</x:v>
       </x:c>
       <x:c r="H17" s="30" t="str">
-        <x:v>Requested Additional Discount %</x:v>
+        <x:v>Requested Total Discount %</x:v>
       </x:c>
       <x:c r="I17" s="30" t="str">
         <x:v>Requested Net Price</x:v>
@@ -747,21 +747,21 @@
       </x:c>
       <x:c r="G18" s="27" t="n">
         <x:f>IFERROR(VLOOKUP(B18,'Reference Data'!$A$2:$F$15,5,FALSE),"")</x:f>
-        <x:v>1704.96</x:v>
+        <x:v>1776</x:v>
       </x:c>
       <x:c r="H18" s="29" t="n">
-        <x:v>0.05</x:v>
+        <x:v>0.09</x:v>
       </x:c>
       <x:c r="I18" s="27" t="n">
-        <x:f>IF(OR(G18="",H18=""),"",G18*(1-H18))</x:f>
-        <x:v>1619.712</x:v>
+        <x:f>IF(OR(E18="",H18=""),"",E18*(1-H18))</x:f>
+        <x:v>1616.16</x:v>
       </x:c>
       <x:c r="J18" s="27" t="n">
         <x:f>IF(OR(D18="",I18=""),"",D18*I18)</x:f>
-        <x:v>161971.2</x:v>
+        <x:v>161616</x:v>
       </x:c>
       <x:c r="K18" s="20" t="str">
-        <x:v>Additional discount supports renewal defense while preserving committed annual volume.</x:v>
+        <x:v>Total discount supports renewal defense while preserving committed annual volume.</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -789,21 +789,21 @@
       </x:c>
       <x:c r="G19" s="27" t="n">
         <x:f>IFERROR(VLOOKUP(B19,'Reference Data'!$A$2:$F$15,5,FALSE),"")</x:f>
-        <x:v>6498</x:v>
+        <x:v>6840</x:v>
       </x:c>
       <x:c r="H19" s="29" t="n">
-        <x:v>0.08</x:v>
+        <x:v>0.13</x:v>
       </x:c>
       <x:c r="I19" s="27" t="n">
-        <x:f>IF(OR(G19="",H19=""),"",G19*(1-H19))</x:f>
-        <x:v>5978.16</x:v>
+        <x:f>IF(OR(E19="",H19=""),"",E19*(1-H19))</x:f>
+        <x:v>5950.8</x:v>
       </x:c>
       <x:c r="J19" s="27" t="n">
         <x:f>IF(OR(D19="",I19=""),"",D19*I19)</x:f>
-        <x:v>149454</x:v>
+        <x:v>148770</x:v>
       </x:c>
       <x:c r="K19" s="20" t="str">
-        <x:v>Requested pricing reflects competitive pressure and the consolidated contract term.</x:v>
+        <x:v>Requested total discount reflects competitive pressure and the consolidated contract term.</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -826,7 +826,7 @@
       </x:c>
       <x:c r="H20" s="29"/>
       <x:c r="I20" s="27" t="str">
-        <x:f>IF(OR(G20="",H20=""),"",G20*(1-H20))</x:f>
+        <x:f>IF(OR(E20="",H20=""),"",E20*(1-H20))</x:f>
       </x:c>
       <x:c r="J20" s="27" t="str">
         <x:f>IF(OR(D20="",I20=""),"",D20*I20)</x:f>
@@ -853,7 +853,7 @@
       </x:c>
       <x:c r="H21" s="29"/>
       <x:c r="I21" s="27" t="str">
-        <x:f>IF(OR(G21="",H21=""),"",G21*(1-H21))</x:f>
+        <x:f>IF(OR(E21="",H21=""),"",E21*(1-H21))</x:f>
       </x:c>
       <x:c r="J21" s="27" t="str">
         <x:f>IF(OR(D21="",I21=""),"",D21*I21)</x:f>
@@ -880,7 +880,7 @@
       </x:c>
       <x:c r="H22" s="29"/>
       <x:c r="I22" s="27" t="str">
-        <x:f>IF(OR(G22="",H22=""),"",G22*(1-H22))</x:f>
+        <x:f>IF(OR(E22="",H22=""),"",E22*(1-H22))</x:f>
       </x:c>
       <x:c r="J22" s="27" t="str">
         <x:f>IF(OR(D22="",I22=""),"",D22*I22)</x:f>
@@ -907,7 +907,7 @@
       </x:c>
       <x:c r="H23" s="29"/>
       <x:c r="I23" s="27" t="str">
-        <x:f>IF(OR(G23="",H23=""),"",G23*(1-H23))</x:f>
+        <x:f>IF(OR(E23="",H23=""),"",E23*(1-H23))</x:f>
       </x:c>
       <x:c r="J23" s="27" t="str">
         <x:f>IF(OR(D23="",I23=""),"",D23*I23)</x:f>
@@ -934,7 +934,7 @@
       </x:c>
       <x:c r="H24" s="29"/>
       <x:c r="I24" s="27" t="str">
-        <x:f>IF(OR(G24="",H24=""),"",G24*(1-H24))</x:f>
+        <x:f>IF(OR(E24="",H24=""),"",E24*(1-H24))</x:f>
       </x:c>
       <x:c r="J24" s="27" t="str">
         <x:f>IF(OR(D24="",I24=""),"",D24*I24)</x:f>
@@ -961,7 +961,7 @@
       </x:c>
       <x:c r="H25" s="29"/>
       <x:c r="I25" s="27" t="str">
-        <x:f>IF(OR(G25="",H25=""),"",G25*(1-H25))</x:f>
+        <x:f>IF(OR(E25="",H25=""),"",E25*(1-H25))</x:f>
       </x:c>
       <x:c r="J25" s="27" t="str">
         <x:f>IF(OR(D25="",I25=""),"",D25*I25)</x:f>
@@ -988,7 +988,7 @@
       </x:c>
       <x:c r="H26" s="29"/>
       <x:c r="I26" s="27" t="str">
-        <x:f>IF(OR(G26="",H26=""),"",G26*(1-H26))</x:f>
+        <x:f>IF(OR(E26="",H26=""),"",E26*(1-H26))</x:f>
       </x:c>
       <x:c r="J26" s="27" t="str">
         <x:f>IF(OR(D26="",I26=""),"",D26*I26)</x:f>
@@ -1015,7 +1015,7 @@
       </x:c>
       <x:c r="H27" s="29"/>
       <x:c r="I27" s="27" t="str">
-        <x:f>IF(OR(G27="",H27=""),"",G27*(1-H27))</x:f>
+        <x:f>IF(OR(E27="",H27=""),"",E27*(1-H27))</x:f>
       </x:c>
       <x:c r="J27" s="27" t="str">
         <x:f>IF(OR(D27="",I27=""),"",D27*I27)</x:f>
@@ -1050,14 +1050,14 @@
       </x:c>
       <x:c r="E30" s="27" t="n">
         <x:f>SUM(J18:J27)</x:f>
-        <x:v>311425.2</x:v>
+        <x:v>310386</x:v>
       </x:c>
       <x:c r="G30" s="15" t="str">
         <x:v>Discount Amount</x:v>
       </x:c>
       <x:c r="H30" s="27" t="n">
         <x:f>B30-E30</x:f>
-        <x:v>37174.79999999999</x:v>
+        <x:v>38214</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -1066,21 +1066,21 @@
       </x:c>
       <x:c r="B31" s="28" t="n">
         <x:f>IF(B30=0,0,H30/B30)</x:f>
-        <x:v>0.10664027538726331</x:v>
+        <x:v>0.10962134251290878</x:v>
       </x:c>
       <x:c r="D31" s="15" t="str">
         <x:v>Gross Profit</x:v>
       </x:c>
       <x:c r="E31" s="27" t="n">
         <x:f>E30-(D18*IFERROR(VLOOKUP(B18,'Reference Data'!$A$2:$F$15,6,FALSE),0)+D19*IFERROR(VLOOKUP(B19,'Reference Data'!$A$2:$F$15,6,FALSE),0)+D20*IFERROR(VLOOKUP(B20,'Reference Data'!$A$2:$F$15,6,FALSE),0)+D21*IFERROR(VLOOKUP(B21,'Reference Data'!$A$2:$F$15,6,FALSE),0)+D22*IFERROR(VLOOKUP(B22,'Reference Data'!$A$2:$F$15,6,FALSE),0)+D23*IFERROR(VLOOKUP(B23,'Reference Data'!$A$2:$F$15,6,FALSE),0)+D24*IFERROR(VLOOKUP(B24,'Reference Data'!$A$2:$F$15,6,FALSE),0)+D25*IFERROR(VLOOKUP(B25,'Reference Data'!$A$2:$F$15,6,FALSE),0)+D26*IFERROR(VLOOKUP(B26,'Reference Data'!$A$2:$F$15,6,FALSE),0)+D27*IFERROR(VLOOKUP(B27,'Reference Data'!$A$2:$F$15,6,FALSE),0))</x:f>
-        <x:v>201925.2</x:v>
+        <x:v>200886</x:v>
       </x:c>
       <x:c r="G31" s="15" t="str">
         <x:v>Gross Margin %</x:v>
       </x:c>
       <x:c r="H31" s="28" t="n">
         <x:f>IF(E30=0,0,E31/E30)</x:f>
-        <x:v>0.6483906890001194</x:v>
+        <x:v>0.6472134696796892</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -1218,7 +1218,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04e34a7e54794f96"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23b87989d7934e11"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1359,7 +1359,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1366a9766fda4365"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39a5ae8d40db48c7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1405,7 +1405,7 @@
         <x:v>Gross Price</x:v>
       </x:c>
       <x:c r="D2" t="str">
-        <x:v>Base Discount %</x:v>
+        <x:v>Base Rebate %</x:v>
       </x:c>
       <x:c r="E2" t="str">
         <x:v>Current Net Price</x:v>
@@ -1437,7 +1437,8 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="E3" s="35" t="n">
-        <x:v>1704.96</x:v>
+        <x:f>C3</x:f>
+        <x:v>1776</x:v>
       </x:c>
       <x:c r="F3" s="35" t="n">
         <x:v>555</x:v>
@@ -1466,7 +1467,8 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="E4" s="35" t="n">
-        <x:v>6498</x:v>
+        <x:f>C4</x:f>
+        <x:v>6840</x:v>
       </x:c>
       <x:c r="F4" s="35" t="n">
         <x:v>2160</x:v>
@@ -1492,7 +1494,8 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="E5" s="35" t="n">
-        <x:v>1064.95</x:v>
+        <x:f>C5</x:f>
+        <x:v>1121</x:v>
       </x:c>
       <x:c r="F5" s="35" t="n">
         <x:v>413</x:v>
@@ -1515,7 +1518,8 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="E6" s="35" t="n">
-        <x:v>371.11199999999997</x:v>
+        <x:f>C6</x:f>
+        <x:v>394.8</x:v>
       </x:c>
       <x:c r="F6" s="35" t="n">
         <x:v>147</x:v>
@@ -1538,7 +1542,8 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="E7" s="35" t="n">
-        <x:v>25811.5</x:v>
+        <x:f>C7</x:f>
+        <x:v>27170</x:v>
       </x:c>
       <x:c r="F7" s="35" t="n">
         <x:v>7150</x:v>
@@ -1561,7 +1566,8 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="E8" s="35" t="n">
-        <x:v>857.375</x:v>
+        <x:f>C8</x:f>
+        <x:v>902.5</x:v>
       </x:c>
       <x:c r="F8" s="35" t="n">
         <x:v>333</x:v>
@@ -1584,7 +1590,8 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="E9" s="35" t="n">
-        <x:v>1166.3519999999999</x:v>
+        <x:f>C9</x:f>
+        <x:v>1240.8</x:v>
       </x:c>
       <x:c r="F9" s="35" t="n">
         <x:v>462</x:v>
@@ -1607,7 +1614,8 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="E10" s="35" t="n">
-        <x:v>884.4499999999999</x:v>
+        <x:f>C10</x:f>
+        <x:v>931</x:v>
       </x:c>
       <x:c r="F10" s="35" t="n">
         <x:v>343</x:v>
@@ -1630,7 +1638,8 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="E11" s="35" t="n">
-        <x:v>8663.039999999999</x:v>
+        <x:f>C11</x:f>
+        <x:v>9024</x:v>
       </x:c>
       <x:c r="F11" s="35" t="n">
         <x:v>2820</x:v>
@@ -1653,7 +1662,8 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="E12" s="35" t="n">
-        <x:v>31407</x:v>
+        <x:f>C12</x:f>
+        <x:v>33060</x:v>
       </x:c>
       <x:c r="F12" s="35" t="n">
         <x:v>8700</x:v>
@@ -1676,7 +1686,8 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="E13" s="35" t="n">
-        <x:v>1155.2</x:v>
+        <x:f>C13</x:f>
+        <x:v>1216</x:v>
       </x:c>
       <x:c r="F13" s="35" t="n">
         <x:v>448</x:v>
@@ -1699,6 +1710,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E14" s="35" t="n">
+        <x:f>C14</x:f>
         <x:v>42000</x:v>
       </x:c>
       <x:c r="F14" s="35" t="n">
@@ -1722,6 +1734,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E15" s="35" t="n">
+        <x:f>C15</x:f>
         <x:v>35000</x:v>
       </x:c>
       <x:c r="F15" s="35" t="n">
@@ -1745,6 +1758,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E16" s="35" t="n">
+        <x:f>C16</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F16" s="35" t="n">
@@ -1790,7 +1804,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcedbe1c766334718"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8eaaeec09ea94000"/>
   </x:tableParts>
 </x:worksheet>
 </file>